--- a/input/Inputfile_2.xlsx
+++ b/input/Inputfile_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bvams\PycharmProjects\salesforce-files-downloader-tool\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bvams\PycharmProjects\salesforce-files-downloader-tool\robot\salesforce-files-downloader-tool\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{362791B2-BB27-42E6-B7EF-4EB0C7024AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55EEA63-6506-4044-A243-557FAFAC371B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,9 +25,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>ContentDocumentID</t>
+  </si>
+  <si>
+    <t>069fj000005fyq9AAA</t>
+  </si>
+  <si>
+    <t>069fj000005fyzpAAA</t>
   </si>
 </sst>
 </file>
@@ -394,13 +400,21 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://workbench.developerforce.com/retrieve.php?id=069fj000005fyq9AAA" xr:uid="{D5C3C3FE-CCE3-46E4-8102-F378B8F31274}"/>
+    <hyperlink ref="A3" r:id="rId2" display="https://workbench.developerforce.com/retrieve.php?id=069fj000005fyzpAAA" xr:uid="{C2507A2D-6ED0-4A90-A4B3-5D5AEFC731C0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
--- a/input/Inputfile_2.xlsx
+++ b/input/Inputfile_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bvams\PycharmProjects\salesforce-files-downloader-tool\robot\salesforce-files-downloader-tool\Input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bvams\PycharmProjects\salesforce-files-downloader-tool\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55EEA63-6506-4044-A243-557FAFAC371B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83E1B0F-E577-41E6-8DFE-6546B7620A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,15 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>ContentDocumentID</t>
-  </si>
-  <si>
-    <t>069fj000005fyq9AAA</t>
-  </si>
-  <si>
-    <t>069fj000005fyzpAAA</t>
   </si>
 </sst>
 </file>
@@ -400,21 +394,13 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A2" s="2"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A3" s="2"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="https://workbench.developerforce.com/retrieve.php?id=069fj000005fyq9AAA" xr:uid="{D5C3C3FE-CCE3-46E4-8102-F378B8F31274}"/>
-    <hyperlink ref="A3" r:id="rId2" display="https://workbench.developerforce.com/retrieve.php?id=069fj000005fyzpAAA" xr:uid="{C2507A2D-6ED0-4A90-A4B3-5D5AEFC731C0}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/input/Inputfile_2.xlsx
+++ b/input/Inputfile_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bvams\PycharmProjects\salesforce-files-downloader-tool\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83E1B0F-E577-41E6-8DFE-6546B7620A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0DFA6D-CA48-4C10-90B2-50FCBD739479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -382,7 +382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.5546875" customWidth="1"/>
@@ -399,6 +399,9 @@
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
     </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
